--- a/02table/TableS7_GWAS_for_SBEIIa_Zm00001d003817.xlsx
+++ b/02table/TableS7_GWAS_for_SBEIIa_Zm00001d003817.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A13950A-F3D8-9641-9CE8-D99C3FD73A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22B3495-B685-B349-8CA0-C53A5009B680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="72080" yWindow="3160" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="550">
   <si>
     <t>Gene</t>
   </si>
@@ -1083,9 +1083,6 @@
     <t>Polyadenylate-binding protein RBP47B</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>Zm00001d051245</t>
   </si>
   <si>
@@ -1573,9 +1570,6 @@
   </si>
   <si>
     <t>Vacuolar protein sorting-associated protein 54 chloroplastic</t>
-  </si>
-  <si>
-    <t>MPH</t>
   </si>
   <si>
     <t>Inbred</t>
@@ -1888,6 +1882,9 @@
       </rPr>
       <t>Physicial position of genes under each GWAS locus.</t>
     </r>
+  </si>
+  <si>
+    <t>DMP</t>
   </si>
   <si>
     <r>
@@ -1912,7 +1909,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> in inbred and hybrid populations, as well as associations with expression heterosis.</t>
+      <t xml:space="preserve"> in inbred and hybrid populations, as well as associations with expression dominance.</t>
     </r>
   </si>
 </sst>
@@ -2343,7 +2340,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2361,46 +2358,46 @@
     </row>
     <row r="2" spans="1:14" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>548</v>
-      </c>
       <c r="K2" s="8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -2423,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -2467,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
@@ -2511,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
@@ -2555,7 +2552,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H6" s="3">
         <v>2</v>
@@ -2599,7 +2596,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H7" s="3">
         <v>2</v>
@@ -2643,7 +2640,7 @@
         <v>1539</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H8" s="3">
         <v>2</v>
@@ -2687,7 +2684,7 @@
         <v>1539</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H9" s="3">
         <v>2</v>
@@ -2731,7 +2728,7 @@
         <v>1539</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H10" s="3">
         <v>2</v>
@@ -2775,7 +2772,7 @@
         <v>1539</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H11" s="3">
         <v>2</v>
@@ -2819,7 +2816,7 @@
         <v>1539</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H12" s="3">
         <v>2</v>
@@ -2863,7 +2860,7 @@
         <v>1539</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H13" s="3">
         <v>2</v>
@@ -2907,7 +2904,7 @@
         <v>1539</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H14" s="3">
         <v>2</v>
@@ -2951,7 +2948,7 @@
         <v>1539</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H15" s="3">
         <v>2</v>
@@ -2995,7 +2992,7 @@
         <v>1539</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H16" s="3">
         <v>2</v>
@@ -3039,7 +3036,7 @@
         <v>1539</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H17" s="3">
         <v>2</v>
@@ -3083,7 +3080,7 @@
         <v>1539</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H18" s="3">
         <v>2</v>
@@ -3127,7 +3124,7 @@
         <v>1539</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H19" s="3">
         <v>2</v>
@@ -3171,7 +3168,7 @@
         <v>1539</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H20" s="3">
         <v>2</v>
@@ -3189,7 +3186,7 @@
         <v>31</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>32</v>
@@ -3215,7 +3212,7 @@
         <v>1539</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H21" s="3">
         <v>2</v>
@@ -3259,7 +3256,7 @@
         <v>1539</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H22" s="3">
         <v>2</v>
@@ -3303,7 +3300,7 @@
         <v>1539</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H23" s="3">
         <v>2</v>
@@ -3347,7 +3344,7 @@
         <v>1539</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H24" s="3">
         <v>2</v>
@@ -3391,7 +3388,7 @@
         <v>1539</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H25" s="3">
         <v>2</v>
@@ -3435,7 +3432,7 @@
         <v>1539</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H26" s="3">
         <v>2</v>
@@ -3479,7 +3476,7 @@
         <v>1539</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H27" s="3">
         <v>2</v>
@@ -3523,7 +3520,7 @@
         <v>1539</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H28" s="3">
         <v>2</v>
@@ -3567,7 +3564,7 @@
         <v>4</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H29" s="3">
         <v>2</v>
@@ -3611,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H30" s="3">
         <v>2</v>
@@ -3655,7 +3652,7 @@
         <v>4</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H31" s="3">
         <v>2</v>
@@ -3673,7 +3670,7 @@
         <v>45</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>46</v>
@@ -3699,7 +3696,7 @@
         <v>356</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H32" s="3">
         <v>2</v>
@@ -3743,7 +3740,7 @@
         <v>356</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H33" s="3">
         <v>2</v>
@@ -3787,7 +3784,7 @@
         <v>356</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H34" s="3">
         <v>2</v>
@@ -3831,7 +3828,7 @@
         <v>356</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H35" s="3">
         <v>2</v>
@@ -3875,7 +3872,7 @@
         <v>356</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H36" s="3">
         <v>2</v>
@@ -3919,7 +3916,7 @@
         <v>356</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H37" s="3">
         <v>2</v>
@@ -3963,7 +3960,7 @@
         <v>356</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H38" s="3">
         <v>2</v>
@@ -4007,7 +4004,7 @@
         <v>356</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
@@ -4051,7 +4048,7 @@
         <v>356</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H40" s="3">
         <v>2</v>
@@ -4095,7 +4092,7 @@
         <v>356</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H41" s="3">
         <v>2</v>
@@ -4139,7 +4136,7 @@
         <v>16</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
@@ -4183,7 +4180,7 @@
         <v>16</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H43" s="3">
         <v>2</v>
@@ -4227,7 +4224,7 @@
         <v>16</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H44" s="3">
         <v>2</v>
@@ -4271,7 +4268,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
@@ -4315,7 +4312,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H46" s="3">
         <v>2</v>
@@ -4359,7 +4356,7 @@
         <v>6</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H47" s="3">
         <v>2</v>
@@ -4403,7 +4400,7 @@
         <v>6</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
@@ -4447,7 +4444,7 @@
         <v>6</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H49" s="3">
         <v>2</v>
@@ -4491,7 +4488,7 @@
         <v>6</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H50" s="3">
         <v>2</v>
@@ -4535,7 +4532,7 @@
         <v>6</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
@@ -4579,7 +4576,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H52" s="3">
         <v>2</v>
@@ -4623,7 +4620,7 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H53" s="3">
         <v>2</v>
@@ -4667,7 +4664,7 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
@@ -4711,7 +4708,7 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H55" s="3">
         <v>2</v>
@@ -4755,7 +4752,7 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H56" s="3">
         <v>2</v>
@@ -4799,7 +4796,7 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
@@ -4843,7 +4840,7 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H58" s="3">
         <v>2</v>
@@ -4861,7 +4858,7 @@
         <v>83</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>84</v>
@@ -4887,7 +4884,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H59" s="3">
         <v>2</v>
@@ -4931,7 +4928,7 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H60" s="3">
         <v>2</v>
@@ -4975,7 +4972,7 @@
         <v>23</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H61" s="3">
         <v>2</v>
@@ -5019,7 +5016,7 @@
         <v>23</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H62" s="3">
         <v>2</v>
@@ -5063,7 +5060,7 @@
         <v>23</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H63" s="3">
         <v>2</v>
@@ -5107,7 +5104,7 @@
         <v>23</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H64" s="3">
         <v>2</v>
@@ -5151,7 +5148,7 @@
         <v>23</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H65" s="3">
         <v>2</v>
@@ -5195,7 +5192,7 @@
         <v>4</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H66" s="3">
         <v>2</v>
@@ -5239,7 +5236,7 @@
         <v>4</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H67" s="3">
         <v>2</v>
@@ -5283,7 +5280,7 @@
         <v>4</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H68" s="3">
         <v>2</v>
@@ -5327,7 +5324,7 @@
         <v>4</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H69" s="3">
         <v>2</v>
@@ -5371,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H70" s="3">
         <v>2</v>
@@ -5415,7 +5412,7 @@
         <v>4</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H71" s="3">
         <v>2</v>
@@ -5459,7 +5456,7 @@
         <v>3</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H72" s="3">
         <v>2</v>
@@ -5503,7 +5500,7 @@
         <v>3</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H73" s="3">
         <v>2</v>
@@ -5547,7 +5544,7 @@
         <v>3</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H74" s="3">
         <v>2</v>
@@ -5591,7 +5588,7 @@
         <v>3</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H75" s="3">
         <v>2</v>
@@ -5609,7 +5606,7 @@
         <v>111</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>112</v>
@@ -5635,7 +5632,7 @@
         <v>757</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H76" s="3">
         <v>2</v>
@@ -5679,7 +5676,7 @@
         <v>757</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H77" s="3">
         <v>2</v>
@@ -5723,7 +5720,7 @@
         <v>757</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H78" s="3">
         <v>2</v>
@@ -5767,7 +5764,7 @@
         <v>757</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H79" s="3">
         <v>2</v>
@@ -5811,7 +5808,7 @@
         <v>757</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H80" s="3">
         <v>2</v>
@@ -5855,7 +5852,7 @@
         <v>757</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H81" s="3">
         <v>2</v>
@@ -5899,7 +5896,7 @@
         <v>757</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H82" s="3">
         <v>2</v>
@@ -5943,7 +5940,7 @@
         <v>757</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H83" s="3">
         <v>2</v>
@@ -5987,7 +5984,7 @@
         <v>757</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H84" s="3">
         <v>2</v>
@@ -6031,7 +6028,7 @@
         <v>757</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H85" s="3">
         <v>2</v>
@@ -6075,7 +6072,7 @@
         <v>757</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H86" s="3">
         <v>2</v>
@@ -6119,7 +6116,7 @@
         <v>757</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H87" s="3">
         <v>2</v>
@@ -6137,7 +6134,7 @@
         <v>31</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>32</v>
@@ -6163,7 +6160,7 @@
         <v>757</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H88" s="3">
         <v>2</v>
@@ -6207,7 +6204,7 @@
         <v>757</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H89" s="3">
         <v>2</v>
@@ -6251,7 +6248,7 @@
         <v>9</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H90" s="3">
         <v>2</v>
@@ -6295,7 +6292,7 @@
         <v>9</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H91" s="3">
         <v>2</v>
@@ -6339,7 +6336,7 @@
         <v>9</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H92" s="3">
         <v>2</v>
@@ -6383,7 +6380,7 @@
         <v>9</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H93" s="3">
         <v>2</v>
@@ -6427,7 +6424,7 @@
         <v>9</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H94" s="3">
         <v>2</v>
@@ -6471,7 +6468,7 @@
         <v>9</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H95" s="3">
         <v>2</v>
@@ -6515,7 +6512,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H96" s="3">
         <v>2</v>
@@ -6559,7 +6556,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H97" s="3">
         <v>2</v>
@@ -6603,7 +6600,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H98" s="3">
         <v>2</v>
@@ -6621,7 +6618,7 @@
         <v>45</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N98" s="1" t="s">
         <v>46</v>
@@ -6647,7 +6644,7 @@
         <v>346</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H99" s="3">
         <v>2</v>
@@ -6691,7 +6688,7 @@
         <v>346</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H100" s="3">
         <v>2</v>
@@ -6735,7 +6732,7 @@
         <v>346</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H101" s="3">
         <v>2</v>
@@ -6779,7 +6776,7 @@
         <v>346</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H102" s="3">
         <v>2</v>
@@ -6823,7 +6820,7 @@
         <v>346</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H103" s="3">
         <v>2</v>
@@ -6867,7 +6864,7 @@
         <v>346</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H104" s="3">
         <v>2</v>
@@ -6911,7 +6908,7 @@
         <v>346</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H105" s="3">
         <v>2</v>
@@ -6955,7 +6952,7 @@
         <v>346</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H106" s="3">
         <v>2</v>
@@ -6999,7 +6996,7 @@
         <v>346</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H107" s="3">
         <v>2</v>
@@ -7043,7 +7040,7 @@
         <v>346</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H108" s="3">
         <v>2</v>
@@ -7087,7 +7084,7 @@
         <v>346</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H109" s="3">
         <v>2</v>
@@ -7131,7 +7128,7 @@
         <v>346</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H110" s="3">
         <v>2</v>
@@ -7175,7 +7172,7 @@
         <v>346</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H111" s="3">
         <v>2</v>
@@ -7219,7 +7216,7 @@
         <v>346</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H112" s="3">
         <v>2</v>
@@ -7263,7 +7260,7 @@
         <v>346</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H113" s="3">
         <v>2</v>
@@ -7307,7 +7304,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H114" s="3">
         <v>2</v>
@@ -7351,7 +7348,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H115" s="3">
         <v>2</v>
@@ -7395,7 +7392,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H116" s="3">
         <v>2</v>
@@ -7439,7 +7436,7 @@
         <v>8</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H117" s="3">
         <v>2</v>
@@ -7483,7 +7480,7 @@
         <v>3</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H118" s="3">
         <v>2</v>
@@ -7527,7 +7524,7 @@
         <v>3</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H119" s="3">
         <v>2</v>
@@ -7571,7 +7568,7 @@
         <v>3</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H120" s="3">
         <v>2</v>
@@ -7615,7 +7612,7 @@
         <v>143</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H121" s="3">
         <v>3</v>
@@ -7659,7 +7656,7 @@
         <v>143</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H122" s="3">
         <v>3</v>
@@ -7703,7 +7700,7 @@
         <v>143</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H123" s="3">
         <v>3</v>
@@ -7747,7 +7744,7 @@
         <v>143</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H124" s="3">
         <v>3</v>
@@ -7791,7 +7788,7 @@
         <v>143</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H125" s="3">
         <v>3</v>
@@ -7835,7 +7832,7 @@
         <v>143</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H126" s="3">
         <v>3</v>
@@ -7879,7 +7876,7 @@
         <v>143</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H127" s="3">
         <v>3</v>
@@ -7923,7 +7920,7 @@
         <v>26</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H128" s="3">
         <v>6</v>
@@ -7967,7 +7964,7 @@
         <v>26</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H129" s="3">
         <v>6</v>
@@ -8011,7 +8008,7 @@
         <v>26</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H130" s="3">
         <v>6</v>
@@ -8055,7 +8052,7 @@
         <v>26</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H131" s="3">
         <v>6</v>
@@ -8099,7 +8096,7 @@
         <v>26</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H132" s="3">
         <v>6</v>
@@ -8143,7 +8140,7 @@
         <v>26</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H133" s="3">
         <v>6</v>
@@ -8187,7 +8184,7 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H134" s="3">
         <v>6</v>
@@ -8231,7 +8228,7 @@
         <v>26</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H135" s="3">
         <v>6</v>
@@ -8275,7 +8272,7 @@
         <v>4</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H136" s="3">
         <v>9</v>
@@ -8319,7 +8316,7 @@
         <v>4</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H137" s="3">
         <v>9</v>
@@ -8363,7 +8360,7 @@
         <v>3</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H138" s="3">
         <v>9</v>
@@ -8407,7 +8404,7 @@
         <v>3</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H139" s="3">
         <v>9</v>
@@ -8451,7 +8448,7 @@
         <v>3</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H140" s="3">
         <v>9</v>
@@ -8495,7 +8492,7 @@
         <v>3</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H141" s="3">
         <v>9</v>
@@ -8539,7 +8536,7 @@
         <v>9</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H142" s="3">
         <v>9</v>
@@ -8583,7 +8580,7 @@
         <v>9</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H143" s="3">
         <v>9</v>
@@ -8627,7 +8624,7 @@
         <v>9</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H144" s="3">
         <v>9</v>
@@ -8671,7 +8668,7 @@
         <v>9</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H145" s="3">
         <v>9</v>
@@ -8715,7 +8712,7 @@
         <v>3</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H146" s="3">
         <v>1</v>
@@ -8759,7 +8756,7 @@
         <v>3</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H147" s="3">
         <v>1</v>
@@ -8803,7 +8800,7 @@
         <v>3</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H148" s="3">
         <v>1</v>
@@ -8847,7 +8844,7 @@
         <v>3</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H149" s="3">
         <v>1</v>
@@ -8891,7 +8888,7 @@
         <v>3</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H150" s="3">
         <v>1</v>
@@ -8935,7 +8932,7 @@
         <v>3</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H151" s="3">
         <v>1</v>
@@ -8979,7 +8976,7 @@
         <v>3</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H152" s="3">
         <v>1</v>
@@ -9023,7 +9020,7 @@
         <v>3</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H153" s="3">
         <v>1</v>
@@ -9067,7 +9064,7 @@
         <v>6</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H154" s="3">
         <v>1</v>
@@ -9111,7 +9108,7 @@
         <v>6</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H155" s="3">
         <v>1</v>
@@ -9155,7 +9152,7 @@
         <v>6</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H156" s="3">
         <v>1</v>
@@ -9199,7 +9196,7 @@
         <v>6</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H157" s="3">
         <v>1</v>
@@ -9243,7 +9240,7 @@
         <v>6</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H158" s="3">
         <v>1</v>
@@ -9287,7 +9284,7 @@
         <v>6</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H159" s="3">
         <v>1</v>
@@ -9331,7 +9328,7 @@
         <v>6</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H160" s="3">
         <v>1</v>
@@ -9375,7 +9372,7 @@
         <v>6</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H161" s="3">
         <v>1</v>
@@ -9419,7 +9416,7 @@
         <v>11</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H162" s="3">
         <v>1</v>
@@ -9463,7 +9460,7 @@
         <v>11</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H163" s="3">
         <v>1</v>
@@ -9507,7 +9504,7 @@
         <v>11</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H164" s="3">
         <v>1</v>
@@ -9551,7 +9548,7 @@
         <v>11</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H165" s="3">
         <v>1</v>
@@ -9595,7 +9592,7 @@
         <v>5</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H166" s="3">
         <v>2</v>
@@ -9613,7 +9610,7 @@
         <v>199</v>
       </c>
       <c r="M166" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N166" s="1" t="s">
         <v>200</v>
@@ -9639,7 +9636,7 @@
         <v>5</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H167" s="3">
         <v>2</v>
@@ -9683,7 +9680,7 @@
         <v>5</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H168" s="3">
         <v>2</v>
@@ -9727,7 +9724,7 @@
         <v>5</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H169" s="3">
         <v>2</v>
@@ -9771,7 +9768,7 @@
         <v>5</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H170" s="3">
         <v>2</v>
@@ -9815,7 +9812,7 @@
         <v>5</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H171" s="3">
         <v>2</v>
@@ -9833,7 +9830,7 @@
         <v>208</v>
       </c>
       <c r="M171" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>209</v>
@@ -9859,7 +9856,7 @@
         <v>5</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H172" s="3">
         <v>2</v>
@@ -9903,7 +9900,7 @@
         <v>5</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H173" s="3">
         <v>2</v>
@@ -9947,7 +9944,7 @@
         <v>10</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H174" s="3">
         <v>2</v>
@@ -9991,7 +9988,7 @@
         <v>10</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H175" s="3">
         <v>2</v>
@@ -10035,7 +10032,7 @@
         <v>10</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H176" s="3">
         <v>2</v>
@@ -10079,7 +10076,7 @@
         <v>10</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H177" s="3">
         <v>2</v>
@@ -10123,7 +10120,7 @@
         <v>10</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H178" s="3">
         <v>2</v>
@@ -10167,7 +10164,7 @@
         <v>10</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H179" s="3">
         <v>2</v>
@@ -10211,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H180" s="3">
         <v>2</v>
@@ -10255,7 +10252,7 @@
         <v>10</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H181" s="3">
         <v>2</v>
@@ -10299,7 +10296,7 @@
         <v>10</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H182" s="3">
         <v>2</v>
@@ -10343,7 +10340,7 @@
         <v>10</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H183" s="3">
         <v>2</v>
@@ -10387,7 +10384,7 @@
         <v>10</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H184" s="3">
         <v>2</v>
@@ -10431,7 +10428,7 @@
         <v>10</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H185" s="3">
         <v>2</v>
@@ -10449,7 +10446,7 @@
         <v>227</v>
       </c>
       <c r="M185" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="N185" s="1" t="s">
         <v>228</v>
@@ -10475,7 +10472,7 @@
         <v>10</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H186" s="3">
         <v>2</v>
@@ -10519,7 +10516,7 @@
         <v>10</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H187" s="3">
         <v>2</v>
@@ -10563,7 +10560,7 @@
         <v>3</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H188" s="3">
         <v>2</v>
@@ -10607,7 +10604,7 @@
         <v>3</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H189" s="3">
         <v>2</v>
@@ -10651,7 +10648,7 @@
         <v>3</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H190" s="3">
         <v>2</v>
@@ -10695,7 +10692,7 @@
         <v>3</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H191" s="3">
         <v>2</v>
@@ -10739,7 +10736,7 @@
         <v>3</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H192" s="3">
         <v>2</v>
@@ -10783,7 +10780,7 @@
         <v>3</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H193" s="3">
         <v>2</v>
@@ -10827,7 +10824,7 @@
         <v>3</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H194" s="3">
         <v>2</v>
@@ -10871,7 +10868,7 @@
         <v>3</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H195" s="3">
         <v>2</v>
@@ -10915,7 +10912,7 @@
         <v>3</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H196" s="3">
         <v>2</v>
@@ -10959,7 +10956,7 @@
         <v>3</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H197" s="3">
         <v>2</v>
@@ -11003,7 +11000,7 @@
         <v>3</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H198" s="3">
         <v>2</v>
@@ -11047,7 +11044,7 @@
         <v>3</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H199" s="3">
         <v>2</v>
@@ -11091,7 +11088,7 @@
         <v>3</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H200" s="3">
         <v>2</v>
@@ -11135,7 +11132,7 @@
         <v>3</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H201" s="3">
         <v>2</v>
@@ -11179,7 +11176,7 @@
         <v>3</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H202" s="3">
         <v>2</v>
@@ -11223,7 +11220,7 @@
         <v>3</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H203" s="3">
         <v>2</v>
@@ -11267,7 +11264,7 @@
         <v>3</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H204" s="3">
         <v>2</v>
@@ -11311,7 +11308,7 @@
         <v>3</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H205" s="3">
         <v>2</v>
@@ -11329,7 +11326,7 @@
         <v>259</v>
       </c>
       <c r="M205" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N205" s="1" t="s">
         <v>260</v>
@@ -11355,7 +11352,7 @@
         <v>3</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H206" s="3">
         <v>2</v>
@@ -11399,7 +11396,7 @@
         <v>3</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H207" s="3">
         <v>2</v>
@@ -11443,7 +11440,7 @@
         <v>3</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H208" s="3">
         <v>2</v>
@@ -11487,7 +11484,7 @@
         <v>3</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H209" s="3">
         <v>2</v>
@@ -11531,7 +11528,7 @@
         <v>3</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H210" s="3">
         <v>2</v>
@@ -11575,7 +11572,7 @@
         <v>3</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H211" s="3">
         <v>2</v>
@@ -11593,7 +11590,7 @@
         <v>269</v>
       </c>
       <c r="M211" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N211" s="1" t="s">
         <v>270</v>
@@ -11619,7 +11616,7 @@
         <v>3</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H212" s="3">
         <v>2</v>
@@ -11663,7 +11660,7 @@
         <v>3</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H213" s="3">
         <v>2</v>
@@ -11707,7 +11704,7 @@
         <v>3</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H214" s="3">
         <v>2</v>
@@ -11751,7 +11748,7 @@
         <v>3</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H215" s="3">
         <v>2</v>
@@ -11795,7 +11792,7 @@
         <v>3</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H216" s="3">
         <v>2</v>
@@ -11839,7 +11836,7 @@
         <v>3</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H217" s="3">
         <v>2</v>
@@ -11857,7 +11854,7 @@
         <v>280</v>
       </c>
       <c r="M217" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N217" s="1" t="s">
         <v>281</v>
@@ -11883,7 +11880,7 @@
         <v>5</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H218" s="3">
         <v>2</v>
@@ -11927,7 +11924,7 @@
         <v>5</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H219" s="3">
         <v>2</v>
@@ -11971,7 +11968,7 @@
         <v>5</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H220" s="3">
         <v>2</v>
@@ -12015,7 +12012,7 @@
         <v>5</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H221" s="3">
         <v>2</v>
@@ -12059,7 +12056,7 @@
         <v>5</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H222" s="3">
         <v>2</v>
@@ -12103,7 +12100,7 @@
         <v>5</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H223" s="3">
         <v>2</v>
@@ -12147,7 +12144,7 @@
         <v>5</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H224" s="3">
         <v>3</v>
@@ -12191,7 +12188,7 @@
         <v>5</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H225" s="3">
         <v>3</v>
@@ -12235,7 +12232,7 @@
         <v>5</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H226" s="3">
         <v>3</v>
@@ -12279,7 +12276,7 @@
         <v>5</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H227" s="3">
         <v>3</v>
@@ -12323,7 +12320,7 @@
         <v>5</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H228" s="3">
         <v>3</v>
@@ -12367,7 +12364,7 @@
         <v>5</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H229" s="3">
         <v>3</v>
@@ -12411,7 +12408,7 @@
         <v>5</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H230" s="3">
         <v>3</v>
@@ -12455,7 +12452,7 @@
         <v>3</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H231" s="3">
         <v>3</v>
@@ -12499,7 +12496,7 @@
         <v>3</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H232" s="3">
         <v>3</v>
@@ -12543,7 +12540,7 @@
         <v>3</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H233" s="3">
         <v>3</v>
@@ -12587,7 +12584,7 @@
         <v>3</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H234" s="3">
         <v>3</v>
@@ -12631,7 +12628,7 @@
         <v>11</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H235" s="3">
         <v>3</v>
@@ -12675,7 +12672,7 @@
         <v>4</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H236" s="3">
         <v>3</v>
@@ -12719,7 +12716,7 @@
         <v>4</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H237" s="3">
         <v>3</v>
@@ -12763,7 +12760,7 @@
         <v>8</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H238" s="3">
         <v>3</v>
@@ -12807,7 +12804,7 @@
         <v>8</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H239" s="3">
         <v>3</v>
@@ -12851,7 +12848,7 @@
         <v>8</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H240" s="3">
         <v>3</v>
@@ -12895,7 +12892,7 @@
         <v>8</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H241" s="3">
         <v>3</v>
@@ -12939,7 +12936,7 @@
         <v>8</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H242" s="3">
         <v>3</v>
@@ -12983,7 +12980,7 @@
         <v>8</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H243" s="3">
         <v>3</v>
@@ -13027,7 +13024,7 @@
         <v>8</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H244" s="3">
         <v>3</v>
@@ -13071,7 +13068,7 @@
         <v>8</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H245" s="3">
         <v>3</v>
@@ -13115,7 +13112,7 @@
         <v>6</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H246" s="3">
         <v>3</v>
@@ -13159,7 +13156,7 @@
         <v>4</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H247" s="3">
         <v>4</v>
@@ -13203,7 +13200,7 @@
         <v>4</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H248" s="3">
         <v>4</v>
@@ -13247,7 +13244,7 @@
         <v>4</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H249" s="3">
         <v>4</v>
@@ -13291,7 +13288,7 @@
         <v>4</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H250" s="3">
         <v>4</v>
@@ -13335,7 +13332,7 @@
         <v>4</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H251" s="3">
         <v>4</v>
@@ -13379,7 +13376,7 @@
         <v>4</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H252" s="3">
         <v>4</v>
@@ -13423,7 +13420,7 @@
         <v>4</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H253" s="3">
         <v>4</v>
@@ -13467,7 +13464,7 @@
         <v>4</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H254" s="3">
         <v>4</v>
@@ -13511,7 +13508,7 @@
         <v>11</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H255" s="3">
         <v>4</v>
@@ -13555,7 +13552,7 @@
         <v>11</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H256" s="3">
         <v>4</v>
@@ -13599,7 +13596,7 @@
         <v>11</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H257" s="3">
         <v>4</v>
@@ -13643,7 +13640,7 @@
         <v>11</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H258" s="3">
         <v>4</v>
@@ -13687,7 +13684,7 @@
         <v>6</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H259" s="3">
         <v>4</v>
@@ -13731,22 +13728,22 @@
         <v>3</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I260" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J260" s="3">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J260" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>350</v>
+        <v>3</v>
       </c>
       <c r="L260" s="3" t="s">
-        <v>350</v>
+        <v>3</v>
       </c>
       <c r="M260" s="3" t="s">
         <v>3</v>
@@ -13775,7 +13772,7 @@
         <v>6</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H261" s="3">
         <v>4</v>
@@ -13790,13 +13787,13 @@
         <v>4</v>
       </c>
       <c r="L261" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="M261" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N261" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="M261" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N261" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.2">
@@ -13819,7 +13816,7 @@
         <v>6</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H262" s="3">
         <v>4</v>
@@ -13834,13 +13831,13 @@
         <v>1</v>
       </c>
       <c r="L262" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="M262" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N262" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="M262" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N262" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.2">
@@ -13863,7 +13860,7 @@
         <v>6</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H263" s="3">
         <v>4</v>
@@ -13878,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M263" s="3" t="s">
         <v>3</v>
@@ -13907,7 +13904,7 @@
         <v>20</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H264" s="3">
         <v>7</v>
@@ -13922,13 +13919,13 @@
         <v>1</v>
       </c>
       <c r="L264" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="M264" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N264" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="M264" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N264" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.2">
@@ -13951,7 +13948,7 @@
         <v>20</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H265" s="3">
         <v>7</v>
@@ -13966,13 +13963,13 @@
         <v>1</v>
       </c>
       <c r="L265" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M265" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N265" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="M265" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N265" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.2">
@@ -13995,7 +13992,7 @@
         <v>20</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H266" s="3">
         <v>7</v>
@@ -14010,13 +14007,13 @@
         <v>1</v>
       </c>
       <c r="L266" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M266" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.2">
@@ -14039,7 +14036,7 @@
         <v>20</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H267" s="3">
         <v>7</v>
@@ -14054,13 +14051,13 @@
         <v>1</v>
       </c>
       <c r="L267" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="M267" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N267" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="M267" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N267" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.2">
@@ -14083,7 +14080,7 @@
         <v>5</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H268" s="3">
         <v>7</v>
@@ -14098,13 +14095,13 @@
         <v>4</v>
       </c>
       <c r="L268" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="M268" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="N268" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="M268" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="N268" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.2">
@@ -14127,7 +14124,7 @@
         <v>5</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H269" s="3">
         <v>7</v>
@@ -14142,7 +14139,7 @@
         <v>1</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M269" s="3" t="s">
         <v>3</v>
@@ -14171,7 +14168,7 @@
         <v>5</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H270" s="3">
         <v>7</v>
@@ -14186,7 +14183,7 @@
         <v>4</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M270" s="3" t="s">
         <v>3</v>
@@ -14215,7 +14212,7 @@
         <v>5</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H271" s="3">
         <v>7</v>
@@ -14230,13 +14227,13 @@
         <v>4</v>
       </c>
       <c r="L271" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="M271" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N271" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="M271" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N271" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.2">
@@ -14259,7 +14256,7 @@
         <v>5</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H272" s="3">
         <v>7</v>
@@ -14274,13 +14271,13 @@
         <v>1</v>
       </c>
       <c r="L272" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M272" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N272" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="M272" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N272" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.2">
@@ -14303,7 +14300,7 @@
         <v>5</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H273" s="3">
         <v>7</v>
@@ -14318,13 +14315,13 @@
         <v>4</v>
       </c>
       <c r="L273" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="M273" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="N273" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="M273" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="N273" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.2">
@@ -14347,7 +14344,7 @@
         <v>5</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H274" s="3">
         <v>7</v>
@@ -14362,13 +14359,13 @@
         <v>4</v>
       </c>
       <c r="L274" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="M274" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N274" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="M274" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N274" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.2">
@@ -14391,7 +14388,7 @@
         <v>5</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H275" s="3">
         <v>7</v>
@@ -14406,13 +14403,13 @@
         <v>4</v>
       </c>
       <c r="L275" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M275" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N275" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="M275" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N275" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.2">
@@ -14435,7 +14432,7 @@
         <v>26</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H276" s="3">
         <v>7</v>
@@ -14450,13 +14447,13 @@
         <v>4</v>
       </c>
       <c r="L276" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M276" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N276" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="M276" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N276" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.2">
@@ -14479,7 +14476,7 @@
         <v>26</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H277" s="3">
         <v>7</v>
@@ -14494,7 +14491,7 @@
         <v>4</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M277" s="3" t="s">
         <v>3</v>
@@ -14523,7 +14520,7 @@
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H278" s="3">
         <v>7</v>
@@ -14538,7 +14535,7 @@
         <v>4</v>
       </c>
       <c r="L278" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M278" s="3" t="s">
         <v>3</v>
@@ -14567,7 +14564,7 @@
         <v>26</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H279" s="3">
         <v>7</v>
@@ -14582,7 +14579,7 @@
         <v>4</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M279" s="3" t="s">
         <v>3</v>
@@ -14611,7 +14608,7 @@
         <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H280" s="3">
         <v>7</v>
@@ -14626,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M280" s="3" t="s">
         <v>3</v>
@@ -14655,7 +14652,7 @@
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H281" s="3">
         <v>7</v>
@@ -14670,7 +14667,7 @@
         <v>4</v>
       </c>
       <c r="L281" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M281" s="3" t="s">
         <v>3</v>
@@ -14699,7 +14696,7 @@
         <v>26</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H282" s="3">
         <v>7</v>
@@ -14714,13 +14711,13 @@
         <v>1</v>
       </c>
       <c r="L282" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="M282" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N282" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="M282" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N282" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.2">
@@ -14743,7 +14740,7 @@
         <v>26</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H283" s="3">
         <v>7</v>
@@ -14758,13 +14755,13 @@
         <v>4</v>
       </c>
       <c r="L283" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M283" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N283" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="M283" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="N283" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.2">
@@ -14787,7 +14784,7 @@
         <v>26</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H284" s="3">
         <v>7</v>
@@ -14802,13 +14799,13 @@
         <v>4</v>
       </c>
       <c r="L284" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="M284" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N284" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="M284" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N284" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.2">
@@ -14831,7 +14828,7 @@
         <v>26</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H285" s="3">
         <v>7</v>
@@ -14846,13 +14843,13 @@
         <v>4</v>
       </c>
       <c r="L285" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="M285" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N285" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="M285" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N285" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.2">
@@ -14875,7 +14872,7 @@
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H286" s="3">
         <v>7</v>
@@ -14890,7 +14887,7 @@
         <v>4</v>
       </c>
       <c r="L286" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M286" s="3" t="s">
         <v>3</v>
@@ -14919,7 +14916,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H287" s="3">
         <v>7</v>
@@ -14934,13 +14931,13 @@
         <v>4</v>
       </c>
       <c r="L287" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="M287" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N287" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="M287" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N287" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.2">
@@ -14963,7 +14960,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H288" s="3">
         <v>7</v>
@@ -14978,13 +14975,13 @@
         <v>4</v>
       </c>
       <c r="L288" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="M288" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N288" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="M288" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N288" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.2">
@@ -15007,7 +15004,7 @@
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H289" s="3">
         <v>7</v>
@@ -15022,13 +15019,13 @@
         <v>4</v>
       </c>
       <c r="L289" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="M289" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N289" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="M289" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N289" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.2">
@@ -15051,7 +15048,7 @@
         <v>26</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H290" s="3">
         <v>7</v>
@@ -15066,13 +15063,13 @@
         <v>4</v>
       </c>
       <c r="L290" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M290" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="N290" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="M290" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="N290" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.2">
@@ -15095,7 +15092,7 @@
         <v>4</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H291" s="3">
         <v>7</v>
@@ -15110,13 +15107,13 @@
         <v>1</v>
       </c>
       <c r="L291" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="M291" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N291" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="M291" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N291" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.2">
@@ -15139,7 +15136,7 @@
         <v>4</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H292" s="3">
         <v>7</v>
@@ -15154,13 +15151,13 @@
         <v>1</v>
       </c>
       <c r="L292" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M292" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N292" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="M292" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N292" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.2">
@@ -15183,7 +15180,7 @@
         <v>4</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H293" s="3">
         <v>7</v>
@@ -15198,13 +15195,13 @@
         <v>1</v>
       </c>
       <c r="L293" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M293" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N293" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="M293" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N293" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.2">
@@ -15227,7 +15224,7 @@
         <v>4</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H294" s="3">
         <v>7</v>
@@ -15242,7 +15239,7 @@
         <v>1</v>
       </c>
       <c r="L294" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M294" s="3" t="s">
         <v>3</v>
@@ -15271,7 +15268,7 @@
         <v>4</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H295" s="3">
         <v>7</v>
@@ -15286,13 +15283,13 @@
         <v>4</v>
       </c>
       <c r="L295" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M295" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N295" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="M295" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N295" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.2">
@@ -15315,7 +15312,7 @@
         <v>4</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H296" s="3">
         <v>7</v>
@@ -15330,13 +15327,13 @@
         <v>4</v>
       </c>
       <c r="L296" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="M296" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="N296" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="M296" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="N296" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.2">
@@ -15359,7 +15356,7 @@
         <v>4</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H297" s="3">
         <v>7</v>
@@ -15374,13 +15371,13 @@
         <v>1</v>
       </c>
       <c r="L297" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="M297" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N297" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="M297" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N297" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.2">
@@ -15403,7 +15400,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H298" s="3">
         <v>7</v>
@@ -15418,7 +15415,7 @@
         <v>4</v>
       </c>
       <c r="L298" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M298" s="3" t="s">
         <v>3</v>
@@ -15447,7 +15444,7 @@
         <v>4</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H299" s="3">
         <v>7</v>
@@ -15462,7 +15459,7 @@
         <v>4</v>
       </c>
       <c r="L299" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M299" s="3" t="s">
         <v>3</v>
@@ -15491,7 +15488,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H300" s="3">
         <v>7</v>
@@ -15506,13 +15503,13 @@
         <v>1</v>
       </c>
       <c r="L300" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="M300" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N300" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="M300" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N300" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.2">
@@ -15535,7 +15532,7 @@
         <v>4</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H301" s="3">
         <v>7</v>
@@ -15550,13 +15547,13 @@
         <v>4</v>
       </c>
       <c r="L301" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="M301" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N301" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="M301" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N301" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.2">
@@ -15579,7 +15576,7 @@
         <v>8</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H302" s="3">
         <v>8</v>
@@ -15594,13 +15591,13 @@
         <v>4</v>
       </c>
       <c r="L302" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M302" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N302" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="M302" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N302" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.2">
@@ -15623,7 +15620,7 @@
         <v>8</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H303" s="3">
         <v>8</v>
@@ -15638,13 +15635,13 @@
         <v>4</v>
       </c>
       <c r="L303" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="M303" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N303" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="M303" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N303" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.2">
@@ -15667,7 +15664,7 @@
         <v>8</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H304" s="3">
         <v>8</v>
@@ -15682,13 +15679,13 @@
         <v>4</v>
       </c>
       <c r="L304" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="M304" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N304" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="M304" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N304" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.2">
@@ -15711,7 +15708,7 @@
         <v>14</v>
       </c>
       <c r="G305" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H305" s="3">
         <v>8</v>
@@ -15726,13 +15723,13 @@
         <v>4</v>
       </c>
       <c r="L305" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="M305" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N305" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="M305" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N305" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.2">
@@ -15755,7 +15752,7 @@
         <v>14</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H306" s="3">
         <v>8</v>
@@ -15770,7 +15767,7 @@
         <v>4</v>
       </c>
       <c r="L306" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M306" s="3" t="s">
         <v>3</v>
@@ -15799,7 +15796,7 @@
         <v>14</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H307" s="3">
         <v>8</v>
@@ -15814,7 +15811,7 @@
         <v>1</v>
       </c>
       <c r="L307" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M307" s="3" t="s">
         <v>3</v>
@@ -15843,7 +15840,7 @@
         <v>14</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H308" s="3">
         <v>8</v>
@@ -15858,13 +15855,13 @@
         <v>4</v>
       </c>
       <c r="L308" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M308" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N308" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="M308" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N308" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.2">
@@ -15887,7 +15884,7 @@
         <v>14</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H309" s="3">
         <v>8</v>
@@ -15902,13 +15899,13 @@
         <v>1</v>
       </c>
       <c r="L309" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="M309" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N309" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="M309" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N309" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.2">
@@ -15931,7 +15928,7 @@
         <v>16</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H310" s="3">
         <v>9</v>
@@ -15946,13 +15943,13 @@
         <v>1</v>
       </c>
       <c r="L310" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="M310" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="N310" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="M310" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="N310" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.2">
@@ -15975,7 +15972,7 @@
         <v>16</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H311" s="3">
         <v>9</v>
@@ -15990,13 +15987,13 @@
         <v>4</v>
       </c>
       <c r="L311" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="M311" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N311" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="M311" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N311" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.2">
@@ -16019,7 +16016,7 @@
         <v>7</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H312" s="3">
         <v>9</v>
@@ -16034,13 +16031,13 @@
         <v>4</v>
       </c>
       <c r="L312" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="M312" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N312" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="M312" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N312" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.2">
@@ -16063,7 +16060,7 @@
         <v>7</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H313" s="3">
         <v>9</v>
@@ -16078,7 +16075,7 @@
         <v>1</v>
       </c>
       <c r="L313" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M313" s="3" t="s">
         <v>3</v>
@@ -16107,7 +16104,7 @@
         <v>7</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H314" s="3">
         <v>9</v>
@@ -16122,7 +16119,7 @@
         <v>4</v>
       </c>
       <c r="L314" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M314" s="3" t="s">
         <v>3</v>
@@ -16151,7 +16148,7 @@
         <v>7</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H315" s="3">
         <v>9</v>
@@ -16166,13 +16163,13 @@
         <v>1</v>
       </c>
       <c r="L315" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="M315" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N315" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="M315" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N315" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.2">
@@ -16195,7 +16192,7 @@
         <v>7</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H316" s="3">
         <v>9</v>
@@ -16210,13 +16207,13 @@
         <v>4</v>
       </c>
       <c r="L316" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="M316" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N316" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="M316" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N316" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.2">
@@ -16239,7 +16236,7 @@
         <v>7</v>
       </c>
       <c r="G317" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H317" s="3">
         <v>9</v>
@@ -16254,13 +16251,13 @@
         <v>4</v>
       </c>
       <c r="L317" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="M317" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N317" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="M317" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N317" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.2">
@@ -16283,7 +16280,7 @@
         <v>79</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H318" s="3">
         <v>9</v>
@@ -16298,13 +16295,13 @@
         <v>1</v>
       </c>
       <c r="L318" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="M318" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N318" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="M318" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N318" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.2">
@@ -16327,7 +16324,7 @@
         <v>79</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H319" s="3">
         <v>9</v>
@@ -16342,13 +16339,13 @@
         <v>1</v>
       </c>
       <c r="L319" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="M319" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N319" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="M319" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N319" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.2">
@@ -16371,7 +16368,7 @@
         <v>79</v>
       </c>
       <c r="G320" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H320" s="3">
         <v>9</v>
@@ -16386,13 +16383,13 @@
         <v>4</v>
       </c>
       <c r="L320" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="M320" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N320" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="M320" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N320" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.2">
@@ -16415,7 +16412,7 @@
         <v>79</v>
       </c>
       <c r="G321" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H321" s="3">
         <v>9</v>
@@ -16430,13 +16427,13 @@
         <v>1</v>
       </c>
       <c r="L321" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="M321" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N321" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="M321" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N321" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.2">
@@ -16459,7 +16456,7 @@
         <v>79</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H322" s="3">
         <v>9</v>
@@ -16474,13 +16471,13 @@
         <v>1</v>
       </c>
       <c r="L322" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="M322" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N322" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="M322" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N322" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.2">
@@ -16503,7 +16500,7 @@
         <v>79</v>
       </c>
       <c r="G323" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H323" s="3">
         <v>9</v>
@@ -16518,7 +16515,7 @@
         <v>4</v>
       </c>
       <c r="L323" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M323" s="3" t="s">
         <v>3</v>
@@ -16547,7 +16544,7 @@
         <v>79</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H324" s="3">
         <v>9</v>
@@ -16562,13 +16559,13 @@
         <v>1</v>
       </c>
       <c r="L324" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="M324" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N324" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="M324" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N324" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.2">
@@ -16591,7 +16588,7 @@
         <v>79</v>
       </c>
       <c r="G325" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H325" s="3">
         <v>9</v>
@@ -16606,13 +16603,13 @@
         <v>1</v>
       </c>
       <c r="L325" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="M325" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N325" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="M325" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N325" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.2">
@@ -16635,7 +16632,7 @@
         <v>79</v>
       </c>
       <c r="G326" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H326" s="3">
         <v>9</v>
@@ -16650,13 +16647,13 @@
         <v>4</v>
       </c>
       <c r="L326" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M326" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N326" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="M326" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N326" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.2">
@@ -16679,7 +16676,7 @@
         <v>79</v>
       </c>
       <c r="G327" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H327" s="3">
         <v>9</v>
@@ -16694,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="L327" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M327" s="3" t="s">
         <v>3</v>
@@ -16723,7 +16720,7 @@
         <v>79</v>
       </c>
       <c r="G328" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H328" s="3">
         <v>9</v>
@@ -16738,13 +16735,13 @@
         <v>1</v>
       </c>
       <c r="L328" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="M328" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N328" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="M328" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N328" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.2">
@@ -16767,7 +16764,7 @@
         <v>8</v>
       </c>
       <c r="G329" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H329" s="3">
         <v>9</v>
@@ -16782,13 +16779,13 @@
         <v>4</v>
       </c>
       <c r="L329" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="M329" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N329" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="M329" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N329" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.2">
@@ -16811,7 +16808,7 @@
         <v>8</v>
       </c>
       <c r="G330" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H330" s="3">
         <v>9</v>
@@ -16826,13 +16823,13 @@
         <v>4</v>
       </c>
       <c r="L330" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="M330" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N330" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="M330" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N330" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.2">
@@ -16855,7 +16852,7 @@
         <v>8</v>
       </c>
       <c r="G331" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H331" s="3">
         <v>9</v>
@@ -16870,7 +16867,7 @@
         <v>4</v>
       </c>
       <c r="L331" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M331" s="3" t="s">
         <v>3</v>
@@ -16899,7 +16896,7 @@
         <v>8</v>
       </c>
       <c r="G332" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H332" s="3">
         <v>9</v>
@@ -16914,7 +16911,7 @@
         <v>4</v>
       </c>
       <c r="L332" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M332" s="3" t="s">
         <v>3</v>
@@ -16943,7 +16940,7 @@
         <v>8</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H333" s="3">
         <v>9</v>
@@ -16958,13 +16955,13 @@
         <v>1</v>
       </c>
       <c r="L333" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M333" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N333" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="M333" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N333" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.2">
@@ -16987,7 +16984,7 @@
         <v>8</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H334" s="3">
         <v>9</v>
@@ -17002,7 +16999,7 @@
         <v>1</v>
       </c>
       <c r="L334" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M334" s="3" t="s">
         <v>3</v>
@@ -17031,7 +17028,7 @@
         <v>8</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H335" s="3">
         <v>9</v>
@@ -17046,13 +17043,13 @@
         <v>4</v>
       </c>
       <c r="L335" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="M335" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N335" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="M335" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N335" s="1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.2">
@@ -17075,7 +17072,7 @@
         <v>8</v>
       </c>
       <c r="G336" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H336" s="3">
         <v>9</v>
@@ -17090,7 +17087,7 @@
         <v>4</v>
       </c>
       <c r="L336" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M336" s="3" t="s">
         <v>3</v>
@@ -17119,7 +17116,7 @@
         <v>8</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H337" s="3">
         <v>9</v>
@@ -17134,7 +17131,7 @@
         <v>1</v>
       </c>
       <c r="L337" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M337" s="3" t="s">
         <v>3</v>
@@ -17163,7 +17160,7 @@
         <v>8</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H338" s="3">
         <v>9</v>
@@ -17178,13 +17175,13 @@
         <v>1</v>
       </c>
       <c r="L338" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="M338" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N338" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="M338" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N338" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.2">
@@ -17207,7 +17204,7 @@
         <v>8</v>
       </c>
       <c r="G339" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H339" s="3">
         <v>9</v>
@@ -17222,13 +17219,13 @@
         <v>1</v>
       </c>
       <c r="L339" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M339" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="N339" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="M339" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="N339" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.2">
@@ -17251,7 +17248,7 @@
         <v>8</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H340" s="3">
         <v>9</v>
@@ -17266,7 +17263,7 @@
         <v>4</v>
       </c>
       <c r="L340" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M340" s="3" t="s">
         <v>3</v>
@@ -17295,7 +17292,7 @@
         <v>8</v>
       </c>
       <c r="G341" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H341" s="3">
         <v>9</v>
@@ -17310,13 +17307,13 @@
         <v>1</v>
       </c>
       <c r="L341" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="M341" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N341" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="M341" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N341" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.2">
@@ -17339,7 +17336,7 @@
         <v>8</v>
       </c>
       <c r="G342" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H342" s="3">
         <v>9</v>
@@ -17354,13 +17351,13 @@
         <v>4</v>
       </c>
       <c r="L342" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="M342" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N342" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="M342" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N342" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.2">
@@ -17383,7 +17380,7 @@
         <v>8</v>
       </c>
       <c r="G343" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H343" s="3">
         <v>9</v>
@@ -17398,7 +17395,7 @@
         <v>1</v>
       </c>
       <c r="L343" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M343" s="3" t="s">
         <v>3</v>
@@ -17427,7 +17424,7 @@
         <v>8</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H344" s="3">
         <v>9</v>
@@ -17442,13 +17439,13 @@
         <v>1</v>
       </c>
       <c r="L344" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="M344" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N344" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="M344" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N344" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.2">
@@ -17471,7 +17468,7 @@
         <v>3</v>
       </c>
       <c r="G345" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H345" s="3">
         <v>9</v>
@@ -17486,13 +17483,13 @@
         <v>4</v>
       </c>
       <c r="L345" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="M345" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N345" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="M345" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N345" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.2">
@@ -17515,7 +17512,7 @@
         <v>3</v>
       </c>
       <c r="G346" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H346" s="3">
         <v>9</v>
@@ -17530,13 +17527,13 @@
         <v>1</v>
       </c>
       <c r="L346" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="M346" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="N346" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="M346" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="N346" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.2">
@@ -17559,7 +17556,7 @@
         <v>3</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H347" s="3">
         <v>9</v>
@@ -17574,13 +17571,13 @@
         <v>4</v>
       </c>
       <c r="L347" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="M347" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N347" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="M347" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N347" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.2">
@@ -17603,7 +17600,7 @@
         <v>3</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H348" s="3">
         <v>9</v>
@@ -17618,13 +17615,13 @@
         <v>1</v>
       </c>
       <c r="L348" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="M348" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="N348" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="M348" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="N348" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.2">
@@ -17647,7 +17644,7 @@
         <v>3</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H349" s="3">
         <v>9</v>
@@ -17662,13 +17659,13 @@
         <v>1</v>
       </c>
       <c r="L349" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="M349" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N349" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="M349" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N349" s="1" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.2">
@@ -17691,7 +17688,7 @@
         <v>5</v>
       </c>
       <c r="G350" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H350" s="3">
         <v>9</v>
@@ -17706,13 +17703,13 @@
         <v>4</v>
       </c>
       <c r="L350" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M350" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N350" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="M350" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N350" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.2">
@@ -17735,7 +17732,7 @@
         <v>5</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H351" s="3">
         <v>9</v>
@@ -17750,13 +17747,13 @@
         <v>4</v>
       </c>
       <c r="L351" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M351" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N351" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="M351" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N351" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.2">
@@ -17779,7 +17776,7 @@
         <v>5</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H352" s="3">
         <v>9</v>
@@ -17794,7 +17791,7 @@
         <v>1</v>
       </c>
       <c r="L352" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M352" s="3" t="s">
         <v>3</v>
@@ -17823,7 +17820,7 @@
         <v>5</v>
       </c>
       <c r="G353" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H353" s="3">
         <v>9</v>
@@ -17838,7 +17835,7 @@
         <v>4</v>
       </c>
       <c r="L353" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M353" s="3" t="s">
         <v>3</v>
@@ -17867,7 +17864,7 @@
         <v>5</v>
       </c>
       <c r="G354" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H354" s="3">
         <v>9</v>
@@ -17882,7 +17879,7 @@
         <v>4</v>
       </c>
       <c r="L354" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M354" s="3" t="s">
         <v>3</v>
@@ -17911,7 +17908,7 @@
         <v>5</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H355" s="3">
         <v>9</v>
@@ -17926,13 +17923,13 @@
         <v>4</v>
       </c>
       <c r="L355" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M355" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N355" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.2">
@@ -17955,7 +17952,7 @@
         <v>3</v>
       </c>
       <c r="G356" s="3" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H356" s="3">
         <v>10</v>
@@ -17970,7 +17967,7 @@
         <v>4</v>
       </c>
       <c r="L356" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M356" s="3" t="s">
         <v>3</v>
@@ -17999,7 +17996,7 @@
         <v>3</v>
       </c>
       <c r="G357" s="5" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H357" s="5">
         <v>10</v>
@@ -18014,38 +18011,38 @@
         <v>4</v>
       </c>
       <c r="L357" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="M357" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N357" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="M357" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N357" s="7" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="359" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="360" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="361" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="362" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="363" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
